--- a/apps/operisflow-api/templates/template_pedido.xlsx
+++ b/apps/operisflow-api/templates/template_pedido.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="_xlfn__FV" vbProcedure="false">NA()</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="Excel_BuiltIn__FilterDatabase" vbProcedure="false">Plan1!$A$13:$J$14</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="Excel_BuiltIn__FilterDatabase" vbProcedure="false">Plan1!$A$15:$J$16</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t xml:space="preserve">PEDIDO 
 REMANU - {mês} {ano}</t>
@@ -36,6 +36,12 @@
   </si>
   <si>
     <t xml:space="preserve">Cliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nome Fantasia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Razão Social</t>
   </si>
   <si>
     <t xml:space="preserve">Endereço</t>
@@ -113,6 +119,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -134,6 +141,7 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -141,12 +149,14 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -154,6 +164,7 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -161,6 +172,7 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -169,24 +181,28 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -194,6 +210,7 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <u val="single"/>
@@ -201,6 +218,7 @@
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -301,7 +319,9 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -500,9 +520,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>5040</xdr:colOff>
+      <xdr:colOff>4680</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>86040</xdr:rowOff>
+      <xdr:rowOff>85680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -516,7 +536,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="39960" y="56880"/>
-          <a:ext cx="1071360" cy="838800"/>
+          <a:ext cx="1071000" cy="838440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -536,15 +556,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultColWidth="9.12890625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E39"/>
+  <sheetFormatPr defaultColWidth="9.13671875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="9.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="14.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="18.25"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="6" style="3" width="9.12"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="6" style="3" width="9.13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -603,7 +623,7 @@
       <c r="E7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="6"/>
@@ -621,7 +641,7 @@
       <c r="E9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="6"/>
@@ -630,7 +650,7 @@
       <c r="E10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="6"/>
@@ -638,91 +658,95 @@
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
     </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="B14" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="C14" s="8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" s="9" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-    </row>
-    <row r="14" s="15" customFormat="true" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="12" t="n">
+      <c r="D14" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" s="9" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" s="15" customFormat="true" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D16" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="14" t="n">
-        <f aca="false">C14*D14</f>
+      <c r="E16" s="14" t="n">
+        <f aca="false">C16*D16</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" s="20" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="17" t="e">
-        <f aca="false">#REF!+#REF!+#REF!+#REF!+#REF!+#REF!+#REF!+#REF!+C14</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D15" s="18" t="n">
-        <f aca="false">SUM(D14:D14)</f>
+    <row r="17" s="20" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="17" t="e">
+        <f aca="false">#REF!+#REF!+#REF!+#REF!+#REF!+#REF!+#REF!+#REF!+C16</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <f aca="false">SUM(D16:D16)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="19" t="n">
-        <f aca="false">SUM(E14:E14)</f>
+      <c r="E17" s="19" t="n">
+        <f aca="false">SUM(E16:E16)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="24"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24"/>
+      <c r="A19" s="24" t="s">
+        <v>15</v>
+      </c>
       <c r="B19" s="24"/>
       <c r="C19" s="24"/>
       <c r="D19" s="24"/>
@@ -763,76 +787,90 @@
       <c r="D24" s="24"/>
       <c r="E24" s="24"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" s="26" t="s">
+      <c r="A26" s="24"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-    </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="25"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="6" t="s">
+      <c r="B27" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="25"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
     </row>
-    <row r="32" s="3" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="33" s="3" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+    </row>
     <row r="34" s="3" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="35" s="3" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="36" s="3" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="37" s="3" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="38" s="3" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="39" s="3" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="22">
     <mergeCell ref="A1:D6"/>
     <mergeCell ref="E1:E6"/>
     <mergeCell ref="B7:E7"/>
@@ -840,22 +878,24 @@
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A17:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:E27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A19:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:E29"/>
     <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B29" r:id="rId1" display="administrativo@evvolantes.com.br "/>
+    <hyperlink ref="B31" r:id="rId1" display="administrativo@evvolantes.com.br "/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.809722222222222" right="0.259722222222222" top="0.859722222222222" bottom="1.32013888888889" header="0.511811023622047" footer="0.511811023622047"/>

--- a/apps/operisflow-api/templates/template_pedido.xlsx
+++ b/apps/operisflow-api/templates/template_pedido.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="_xlfn__FV" vbProcedure="false">NA()</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="Excel_BuiltIn__FilterDatabase" vbProcedure="false">Plan1!$A$15:$J$16</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="Excel_BuiltIn__FilterDatabase" vbProcedure="false">Plan1!$A$20:$J$21</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -24,83 +24,108 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
   <si>
     <t xml:space="preserve">PEDIDO 
 REMANU - {mês} {ano}</t>
   </si>
   <si>
-    <t xml:space="preserve">PEDIDO 
-Nº {numero}
+    <t xml:space="preserve">PEDIDO Nº {numero}
 {data}</t>
   </si>
   <si>
-    <t xml:space="preserve">Cliente</t>
+    <t xml:space="preserve">Razão Social</t>
   </si>
   <si>
     <t xml:space="preserve">Nome Fantasia</t>
   </si>
   <si>
-    <t xml:space="preserve">Razão Social</t>
+    <t xml:space="preserve">CNPJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-mail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel (Comer):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel (Pessoal):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rua e Nº</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bairro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estado / UF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cep:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IE (Inscrição Estadual)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IM (Inscrição Municipal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CÓDIGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESCRIÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDIDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          CONDIÇÕES DE PAGAMENTO: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beneficiário</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV VOLANTES</t>
   </si>
   <si>
     <t xml:space="preserve">Endereço</t>
   </si>
   <si>
-    <t xml:space="preserve">CNPJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-mail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CÓDIGO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DESCRIÇÃO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEDIDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          CONDIÇÕES DE PAGAMENTO: TOTAL: R$                                                 BOLETOS:                                                                                                
-BANCO C6 (336), AGÊNCIA: 0001, CONTA CORRENTE: 38637762-6, 
+    <t xml:space="preserve">Rua Yoshikatsu Lida, 12 Residencial Sol Nascente SJ dos Campos – SP – Cep:12236-072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.144.715/0001-95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-MAIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">administrativo@evvolantes.com.br </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel (Comer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(12) 982668702 (Comercial / Adm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(12) 98135-0009 (Eudes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dados Bancários</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANCO C6 (336), AGÊNCIA: 0001, CONTA CORRENTE: 38637762-6, 
 PIX: 3b7492d3-8dd7-4e14-a6fd-d8bd9c5f0d19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beneficiário</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUDES VOLANTES  LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rua Yoshikatsu Lida, 12 Residencial Sol Nascente SJ dos Campos – SP – Cep:12236-072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.144.715/0001-95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-MAIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">administrativo@evvolantes.com.br </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEL.:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(12) 98135-0009 (Eudes)</t>
   </si>
 </sst>
 </file>
@@ -113,7 +138,7 @@
     <numFmt numFmtId="166" formatCode="&quot;R$ &quot;#,##0.00"/>
     <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -217,6 +242,14 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -323,7 +356,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -433,6 +466,10 @@
       <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -520,9 +557,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>4680</xdr:colOff>
+      <xdr:colOff>3960</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>85680</xdr:rowOff>
+      <xdr:rowOff>84960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -536,7 +573,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="39960" y="56880"/>
-          <a:ext cx="1071000" cy="838440"/>
+          <a:ext cx="1070280" cy="837720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -556,14 +593,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultColWidth="9.13671875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="9.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="14.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="18.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="36.4"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="6" style="3" width="9.13"/>
   </cols>
   <sheetData>
@@ -668,7 +705,7 @@
       <c r="E12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="6"/>
@@ -676,112 +713,122 @@
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" customFormat="false" ht="26.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" customFormat="false" ht="26.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" s="9" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-    </row>
-    <row r="16" s="15" customFormat="true" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="12" t="n">
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" s="9" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" s="15" customFormat="true" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D21" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="14" t="n">
-        <f aca="false">C16*D16</f>
+      <c r="E21" s="14" t="n">
+        <f aca="false">C21*D21</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" s="20" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="17" t="e">
-        <f aca="false">#REF!+#REF!+#REF!+#REF!+#REF!+#REF!+#REF!+#REF!+C16</f>
+    <row r="22" s="20" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="16"/>
+      <c r="C22" s="17" t="e">
+        <f aca="false">#REF!+#REF!+#REF!+#REF!+#REF!+#REF!+#REF!+#REF!+C21</f>
         <v>#REF!</v>
       </c>
-      <c r="D17" s="18" t="n">
-        <f aca="false">SUM(D16:D16)</f>
+      <c r="D22" s="18" t="n">
+        <f aca="false">SUM(D21:D21)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="19" t="n">
-        <f aca="false">SUM(E16:E16)</f>
+      <c r="E22" s="19" t="n">
+        <f aca="false">SUM(E21:E21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="24"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="24"/>
+      <c r="A24" s="24" t="s">
+        <v>20</v>
+      </c>
       <c r="B24" s="24"/>
       <c r="C24" s="24"/>
       <c r="D24" s="24"/>
@@ -801,76 +848,153 @@
       <c r="D26" s="24"/>
       <c r="E26" s="24"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="24"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-    </row>
-    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="25"/>
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B31" s="27" t="s">
+      <c r="A28" s="24"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="24"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="24"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="s">
+      <c r="B32" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
     </row>
-    <row r="34" s="3" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="35" s="3" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="36" s="3" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="37" s="3" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="38" s="3" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="39" s="3" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+    </row>
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="25"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B36" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+    </row>
+    <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>132482429119</v>
+      </c>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>455637</v>
+      </c>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="34.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" s="28"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
+    </row>
+    <row r="42" s="3" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="43" s="3" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="44" s="3" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="45" s="3" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="31">
     <mergeCell ref="A1:D6"/>
     <mergeCell ref="E1:E6"/>
     <mergeCell ref="B7:E7"/>
@@ -880,22 +1004,31 @@
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B13:E13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A19:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A24:E31"/>
     <mergeCell ref="B32:E32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B31" r:id="rId1" display="administrativo@evvolantes.com.br "/>
+    <hyperlink ref="B36" r:id="rId1" display="administrativo@evvolantes.com.br "/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.809722222222222" right="0.259722222222222" top="0.859722222222222" bottom="1.32013888888889" header="0.511811023622047" footer="0.511811023622047"/>
